--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753997</v>
+        <v>121754041</v>
       </c>
       <c r="B2" t="n">
         <v>92004</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528177</v>
+        <v>528139</v>
       </c>
       <c r="R2" t="n">
-        <v>6344467</v>
+        <v>6344413</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R3" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754041</v>
+        <v>121754254</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528139</v>
+        <v>527999</v>
       </c>
       <c r="R4" t="n">
-        <v>6344413</v>
+        <v>6344606</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R3" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R4" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R3" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R4" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754041</v>
+        <v>121753997</v>
       </c>
       <c r="B2" t="n">
         <v>92004</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528139</v>
+        <v>528177</v>
       </c>
       <c r="R2" t="n">
-        <v>6344413</v>
+        <v>6344467</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R3" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754254</v>
+        <v>121754041</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527999</v>
+        <v>528139</v>
       </c>
       <c r="R4" t="n">
-        <v>6344606</v>
+        <v>6344413</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R2" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R3" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R2" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753997</v>
+        <v>121754041</v>
       </c>
       <c r="B3" t="n">
         <v>92004</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528177</v>
+        <v>528139</v>
       </c>
       <c r="R3" t="n">
-        <v>6344467</v>
+        <v>6344413</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754041</v>
+        <v>121754254</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528139</v>
+        <v>527999</v>
       </c>
       <c r="R4" t="n">
-        <v>6344413</v>
+        <v>6344606</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R2" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R4" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>92018</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R2" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +780,7 @@
         <v>121754041</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B4" t="n">
-        <v>92004</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R4" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B2" t="n">
-        <v>92018</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R2" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -780,7 +785,7 @@
         <v>121754041</v>
       </c>
       <c r="B3" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>92020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R4" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121754254</v>
+        <v>121753997</v>
       </c>
       <c r="B2" t="n">
-        <v>57518</v>
+        <v>92021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527999</v>
+        <v>528177</v>
       </c>
       <c r="R2" t="n">
-        <v>6344606</v>
+        <v>6344467</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +780,7 @@
         <v>121754041</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121753997</v>
+        <v>121754254</v>
       </c>
       <c r="B4" t="n">
-        <v>92020</v>
+        <v>57518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528177</v>
+        <v>527999</v>
       </c>
       <c r="R4" t="n">
-        <v>6344467</v>
+        <v>6344606</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121753997</v>
       </c>
       <c r="B2" t="n">
-        <v>92021</v>
+        <v>92030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121754041</v>
+        <v>121754254</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>57522</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stora Höghult, Stora Höghult, Sm</t>
+          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528139</v>
+        <v>527999</v>
       </c>
       <c r="R3" t="n">
-        <v>6344413</v>
+        <v>6344606</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121754254</v>
+        <v>121754041</v>
       </c>
       <c r="B4" t="n">
-        <v>57518</v>
+        <v>92030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Höghult södra naturreservat, Höghult södra naturreservat, Sm</t>
+          <t>Stora Höghult, Stora Höghult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527999</v>
+        <v>528139</v>
       </c>
       <c r="R4" t="n">
-        <v>6344606</v>
+        <v>6344413</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 28300-2024 artfynd.xlsx
+++ b/artfynd/A 28300-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121753997</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121754041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121753935</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,8 +1090,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121754254</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>